--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:29</t>
+          <t>2026-09-09 00:51:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:30</t>
+          <t>2026-09-09 00:51:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:31</t>
+          <t>2026-09-09 00:51:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:32</t>
+          <t>2026-09-09 00:51:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:32</t>
+          <t>2026-09-09 00:51:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:32</t>
+          <t>2026-09-09 00:51:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:32</t>
+          <t>2026-09-09 00:51:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:32</t>
+          <t>2026-09-09 00:51:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:38</t>
+          <t>2026-09-09 01:17:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:39</t>
+          <t>2026-09-09 01:17:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:40</t>
+          <t>2026-09-09 01:17:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:41</t>
+          <t>2026-09-09 01:17:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:41</t>
+          <t>2026-09-09 01:17:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:41</t>
+          <t>2026-09-09 01:17:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:41</t>
+          <t>2026-09-09 01:17:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:41</t>
+          <t>2026-09-09 01:17:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.86%2155</t>
+          <t>+6.5%2295</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2155</v>
+        <v>2295</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1955</v>
+        <v>2015</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:39</t>
+          <t>2026-09-09 19:34:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19220</v>
+        <v>18605</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5550</v>
+        <v>5760</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1225</v>
+        <v>1345</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1385</v>
+        <v>1330</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4.32%3620</t>
+          <t>-0.28%3610</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3620</v>
+        <v>3610</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.68%291</t>
+          <t>+0.52%292.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>291</v>
+        <v>292.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:40</t>
+          <t>2026-09-09 19:34:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.13%2635</t>
+          <t>-3.04%2555</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2635</v>
+        <v>2555</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.32%1490</t>
+          <t>-2.35%1455</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.2%907</t>
+          <t>+0.99%916</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.78%717</t>
+          <t>+1.81%730</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.95%235</t>
+          <t>+0.64%236.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>235</v>
+        <v>236.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.11%534</t>
+          <t>+1.69%543</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>+1.69%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.18%112</t>
+          <t>+3.57%116</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+9.92%2825</t>
+          <t>-1.59%2780</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2825</v>
+        <v>2780</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.28%708</t>
+          <t>0%708</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+6.04%1405</t>
+          <t>-4.27%1345</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1405</v>
+        <v>1345</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.49%1370</t>
+          <t>-1.09%1355</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1370</v>
+        <v>1355</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.02%931</t>
+          <t>+7.3%999</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>931</v>
+        <v>999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.21%286</t>
+          <t>+0.52%287.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>286</v>
+        <v>287.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.48%2085</t>
+          <t>0%2085</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:42</t>
+          <t>2026-09-09 19:34:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.49%414</t>
+          <t>+0.12%414.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>414</v>
+        <v>414.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:43</t>
+          <t>2026-09-09 19:34:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%692</t>
+          <t>+1.88%705</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>705</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:43</t>
+          <t>2026-09-09 19:34:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3317,17 +3317,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.66%532</t>
+          <t>+0.56%535</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>535</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:43</t>
+          <t>2026-09-09 19:34:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+4.44%188</t>
+          <t>-2.66%183</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:43</t>
+          <t>2026-09-09 19:34:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.55%1335</t>
+          <t>-0.37%1330</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:43</t>
+          <t>2026-09-09 19:34:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3506,17 +3506,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.72%139</t>
+          <t>+0.36%139.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:19</t>
+          <t>2026-09-09 22:37:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:21</t>
+          <t>2026-09-09 22:37:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:22</t>
+          <t>2026-09-09 22:37:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:23</t>
+          <t>2026-09-09 22:37:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:23</t>
+          <t>2026-09-09 22:37:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:23</t>
+          <t>2026-09-09 22:37:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:23</t>
+          <t>2026-09-09 22:37:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:23</t>
+          <t>2026-09-09 22:37:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:44</t>
+          <t>2026-09-09 22:49:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:45</t>
+          <t>2026-09-09 22:49:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:46</t>
+          <t>2026-09-09 22:49:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:48</t>
+          <t>2026-09-09 22:49:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:48</t>
+          <t>2026-09-09 22:49:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:48</t>
+          <t>2026-09-09 22:49:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:48</t>
+          <t>2026-09-09 22:49:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:48</t>
+          <t>2026-09-09 22:49:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:37</t>
+          <t>2026-09-09 23:10:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:38</t>
+          <t>2026-09-09 23:10:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:40</t>
+          <t>2026-09-09 23:10:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:41</t>
+          <t>2026-09-09 23:10:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:41</t>
+          <t>2026-09-09 23:10:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:41</t>
+          <t>2026-09-09 23:10:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:41</t>
+          <t>2026-09-09 23:10:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:41</t>
+          <t>2026-09-09 23:10:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
